--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92557701813</v>
+        <v>46157.93060160283</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93060160283</v>
+        <v>46157.9314450253</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.9314450253</v>
+        <v>46157.93389518547</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93389518547</v>
+        <v>46157.93702157218</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93702157218</v>
+        <v>46158.28207096968</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28207096968</v>
+        <v>46158.29659876478</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29659876478</v>
+        <v>46158.2979882131</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.2979882131</v>
+        <v>46158.33375844707</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33375844707</v>
+        <v>46158.36842603496</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36842603496</v>
+        <v>46158.37277989282</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
